--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(2).xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity Projects\VNovelizerTest_v1.0\Assets\Resources\VNovelizerRes\ExcelVNScripts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17415" windowHeight="7680"/>
+    <workbookView windowWidth="20685" windowHeight="11715"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线313-315（中）" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="441">
   <si>
     <t>ID</t>
   </si>
@@ -82,6 +87,9 @@
     <t>不是从窗户外面、也不是从你们腰间的无线电，而是来自床头柜上的一台老式录音机。</t>
   </si>
   <si>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
@@ -673,7 +681,10 @@
     <t>“啪嗒。”</t>
   </si>
   <si>
-    <t>bgfade(sntzm_david313-315(2)_62,1)</t>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>parallel(playsfx(Kata);bgfade(sntzm_david313-315(2)_62,1))</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=58</t>
@@ -683,6 +694,9 @@
   </si>
   <si>
     <t>一声轻响，从床头柜的方向传来。</t>
+  </si>
+  <si>
+    <t>8 enhanced suspence-horror</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=59</t>
@@ -2618,7 +2632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="27" spans="1:12">
+    <row r="2" ht="45" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2644,30 +2658,30 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -2676,7 +2690,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -2688,15 +2702,15 @@
         <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" ht="42" spans="1:12">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2705,7 +2719,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -2714,7 +2728,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2726,15 +2740,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:12">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2752,7 +2766,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2764,15 +2778,15 @@
         <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2790,7 +2804,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2805,12 +2819,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:12">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2828,7 +2842,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2843,12 +2857,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="40.5" spans="1:12">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2866,7 +2880,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2877,17 +2891,16 @@
       <c r="J8" t="s">
         <v>15</v>
       </c>
-      <c r="K8"/>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="58.5" spans="1:12">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -2902,7 +2915,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2914,15 +2927,15 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="27" spans="1:12">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2940,7 +2953,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2955,15 +2968,15 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -2978,7 +2991,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -2993,15 +3006,15 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" ht="69" spans="1:12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -3016,7 +3029,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3031,12 +3044,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="40.5" spans="1:12">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3054,7 +3067,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3069,15 +3082,15 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="57" spans="1:12">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -3092,7 +3105,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3107,15 +3120,15 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="54" spans="1:12">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -3130,7 +3143,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3145,12 +3158,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="40.5" spans="1:12">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3168,7 +3181,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3183,15 +3196,15 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" ht="40.5" spans="1:12">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -3206,7 +3219,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3221,15 +3234,15 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -3244,7 +3257,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3259,15 +3272,15 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" ht="57" spans="1:12">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3282,7 +3295,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3297,15 +3310,15 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="42" spans="1:12">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
@@ -3320,7 +3333,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3335,12 +3348,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="67.5" spans="1:12">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3358,7 +3371,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3373,15 +3386,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:12">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3396,7 +3409,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3411,12 +3424,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" ht="40.5" spans="1:12">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3434,7 +3447,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3449,15 +3462,15 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" ht="42" spans="1:12">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -3472,7 +3485,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3487,15 +3500,15 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" ht="27" spans="1:12">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -3510,7 +3523,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3525,12 +3538,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" ht="40.5" spans="1:12">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3548,7 +3561,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3563,15 +3576,15 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -3586,7 +3599,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3601,15 +3614,15 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" ht="54" spans="1:12">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3624,7 +3637,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3639,12 +3652,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:12">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3662,7 +3675,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3677,15 +3690,15 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" ht="27" spans="1:12">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -3700,7 +3713,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3715,12 +3728,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" ht="54" spans="1:12">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3738,7 +3751,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3753,12 +3766,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" ht="40.5" spans="1:12">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3776,7 +3789,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3791,12 +3804,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3814,7 +3827,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3825,14 +3838,13 @@
       <c r="J33" t="s">
         <v>15</v>
       </c>
-      <c r="K33"/>
       <c r="L33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" ht="30" spans="1:12">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3850,7 +3862,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3862,15 +3874,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" ht="27" spans="1:12">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3888,7 +3900,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3903,15 +3915,15 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -3926,7 +3938,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3941,21 +3953,21 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:12">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -3964,7 +3976,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3976,24 +3988,24 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" ht="30" spans="1:12">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4002,7 +4014,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4014,15 +4026,15 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" ht="27" spans="1:12">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4040,7 +4052,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4055,12 +4067,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" ht="55.5" spans="1:12">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4078,7 +4090,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4093,12 +4105,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" ht="28.5" spans="1:12">
       <c r="A41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4116,7 +4128,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4131,12 +4143,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" ht="27" spans="1:12">
       <c r="A42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4154,7 +4166,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4169,12 +4181,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:12">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4192,7 +4204,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4207,15 +4219,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" ht="30" spans="1:12">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4230,7 +4242,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4242,15 +4254,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" ht="55.5" spans="1:12">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4268,7 +4280,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4283,12 +4295,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4321,12 +4333,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" ht="90" spans="1:12">
       <c r="A47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4344,7 +4356,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4356,18 +4368,18 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:12">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -4382,7 +4394,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4397,21 +4409,21 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" ht="57" spans="1:12">
       <c r="A49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4420,7 +4432,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4432,15 +4444,15 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" ht="90" spans="1:12">
       <c r="A50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4458,7 +4470,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4470,18 +4482,18 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" ht="54" spans="1:12">
       <c r="A51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -4496,7 +4508,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4511,21 +4523,21 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" ht="55.5" spans="1:12">
       <c r="A52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4534,7 +4546,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4546,15 +4558,15 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" ht="30" spans="1:12">
       <c r="A53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4563,7 +4575,7 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4572,7 +4584,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4587,21 +4599,21 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" ht="55.5" spans="1:12">
       <c r="A54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4610,7 +4622,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4625,12 +4637,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" ht="54" spans="1:12">
       <c r="A55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4639,7 +4651,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4648,7 +4660,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4660,15 +4672,15 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4686,7 +4698,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4701,12 +4713,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" ht="69" spans="1:12">
       <c r="A57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4724,7 +4736,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4739,12 +4751,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" ht="55.5" spans="1:12">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4762,7 +4774,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4777,12 +4789,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4800,7 +4812,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4815,12 +4827,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" ht="40.5" spans="1:12">
       <c r="A60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4838,7 +4850,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4853,12 +4865,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" ht="40.5" spans="1:12">
       <c r="A61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4876,7 +4888,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4891,12 +4903,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" ht="60" spans="1:12">
       <c r="A62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4914,14 +4926,11 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
       </c>
-      <c r="I62" t="s">
-        <v>15</v>
-      </c>
       <c r="J62" t="s">
         <v>15</v>
       </c>
@@ -4929,12 +4938,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4952,27 +4961,27 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>15</v>
+        <v>215</v>
       </c>
       <c r="J63" t="s">
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L63" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="64" ht="30" spans="1:12">
       <c r="A64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -4990,13 +4999,13 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>15</v>
+        <v>220</v>
       </c>
       <c r="J64" t="s">
         <v>15</v>
@@ -5005,12 +5014,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" ht="55.5" spans="1:12">
       <c r="A65" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5028,7 +5037,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5043,21 +5052,21 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5066,7 +5075,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5078,15 +5087,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L66" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5095,7 +5104,7 @@
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -5104,7 +5113,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5116,15 +5125,15 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L67" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5142,7 +5151,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5157,12 +5166,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" ht="27" spans="1:12">
       <c r="A69" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5180,7 +5189,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5195,12 +5204,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" ht="42" spans="1:12">
       <c r="A70" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5218,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5230,15 +5239,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="L70" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5271,12 +5280,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" ht="90" spans="1:12">
       <c r="A72" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5294,7 +5303,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5306,15 +5315,15 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L72" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73" ht="90" spans="1:12">
       <c r="A73" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5332,7 +5341,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5347,12 +5356,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" ht="27" spans="1:12">
       <c r="A74" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5370,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5385,12 +5394,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75" ht="42" spans="1:12">
       <c r="A75" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5408,7 +5417,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5423,21 +5432,21 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="76" ht="30" spans="1:12">
       <c r="A76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -5446,7 +5455,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5458,15 +5467,15 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" ht="30" spans="1:12">
       <c r="A77" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5475,7 +5484,7 @@
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -5484,7 +5493,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5496,15 +5505,15 @@
         <v>15</v>
       </c>
       <c r="K77" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L77" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" ht="43.5" spans="1:12">
       <c r="A78" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5522,7 +5531,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5534,10 +5543,10 @@
         <v>15</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L78" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -5558,55 +5567,55 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B5" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5614,50 +5623,50 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:2">
       <c r="A11" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" ht="60" spans="1:2">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" ht="75" spans="1:2">
       <c r="A13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -5679,616 +5688,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E6" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D8" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F8" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C10" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E10" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F10" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C11" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F11" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B12" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C12" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D12" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C13" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D13" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E13" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F13" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B14" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C14" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E14" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F14" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B15" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C15" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D15" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E15" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F15" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B16" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C16" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D16" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E16" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F16" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B17" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C17" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B18" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C18" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D18" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E18" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F18" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B19" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C19" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D19" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E19" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F19" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B20" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C20" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E20" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F20" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B21" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C21" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D21" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E21" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F21" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B22" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C22" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D22" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E22" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F22" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B23" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C23" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D23" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E23" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F23" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B24" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C24" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D24" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E24" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F24" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B25" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C25" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D25" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E25" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F25" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B26" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C26" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D26" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E26" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F26" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B27" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C27" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D27" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E27" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F27" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B28" t="s">
+        <v>423</v>
+      </c>
+      <c r="C28" t="s">
+        <v>424</v>
+      </c>
+      <c r="D28" t="s">
         <v>420</v>
       </c>
-      <c r="C28" t="s">
-        <v>421</v>
-      </c>
-      <c r="D28" t="s">
-        <v>417</v>
-      </c>
       <c r="E28" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F28" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B29" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C29" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D29" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E29" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F29" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B30" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C30" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D30" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E30" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F30" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B31" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C31" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D31" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11715"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线313-315（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="442">
   <si>
     <t>ID</t>
   </si>
@@ -93,7 +93,7 @@
     <t>false</t>
   </si>
   <si>
-    <t>bgfade(sntzm_david313-315(2)_1,1)</t>
+    <t>bgfade(sntzm_david313-315(2)_1,1)&amp;unlockmusic(Music7)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=0</t>
@@ -540,7 +540,54 @@
     <t>parallel(memoryoff();bgfade(sntzm_david313-315(2)_33,1))</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=45; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"追问","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=45; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>追问</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>48</t>
@@ -697,6 +744,9 @@
   </si>
   <si>
     <t>8 enhanced suspence-horror</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music8)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=59</t>
@@ -1428,6 +1478,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1580,11 +1635,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1893,31 +1943,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1926,124 +1973,130 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4370,7 +4423,7 @@
       <c r="K47" t="s">
         <v>167</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" s="2" t="s">
         <v>168</v>
       </c>
     </row>
@@ -5011,15 +5064,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="L64" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" ht="55.5" spans="1:12">
       <c r="A65" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5037,7 +5090,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5052,12 +5105,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B66" t="s">
         <v>22</v>
@@ -5075,7 +5128,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5090,12 +5143,12 @@
         <v>25</v>
       </c>
       <c r="L66" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5113,7 +5166,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5128,12 +5181,12 @@
         <v>29</v>
       </c>
       <c r="L67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5151,7 +5204,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5166,12 +5219,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" ht="27" spans="1:12">
       <c r="A69" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5189,7 +5242,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5204,12 +5257,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="70" ht="42" spans="1:12">
       <c r="A70" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5227,7 +5280,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5239,15 +5292,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L70" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5280,12 +5333,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" ht="90" spans="1:12">
       <c r="A72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5303,7 +5356,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5315,15 +5368,15 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="73" ht="90" spans="1:12">
       <c r="A73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5341,7 +5394,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5356,12 +5409,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" ht="27" spans="1:12">
       <c r="A74" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5379,7 +5432,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5394,12 +5447,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75" ht="42" spans="1:12">
       <c r="A75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5417,7 +5470,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5432,12 +5485,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" ht="30" spans="1:12">
       <c r="A76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
@@ -5455,7 +5508,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5470,12 +5523,12 @@
         <v>25</v>
       </c>
       <c r="L76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="77" ht="30" spans="1:12">
       <c r="A77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5493,7 +5546,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5508,12 +5561,12 @@
         <v>29</v>
       </c>
       <c r="L77" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="78" ht="43.5" spans="1:12">
       <c r="A78" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5531,7 +5584,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5542,11 +5595,11 @@
       <c r="J78" t="s">
         <v>15</v>
       </c>
-      <c r="K78" s="2" t="s">
-        <v>264</v>
+      <c r="K78" s="3" t="s">
+        <v>265</v>
       </c>
       <c r="L78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -5567,47 +5620,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -5615,7 +5668,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5623,7 +5676,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B8" t="s">
         <v>115</v>
@@ -5631,7 +5684,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B9" t="s">
         <v>81</v>
@@ -5639,34 +5692,34 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:2">
       <c r="A11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" ht="60" spans="1:2">
       <c r="A12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" ht="75" spans="1:2">
       <c r="A13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -5688,616 +5741,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B15" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C15" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F17" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B18" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E18" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D19" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F19" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B20" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C20" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D20" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E20" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F20" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D21" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E21" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F21" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B22" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C22" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D22" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E22" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F22" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B23" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C23" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D23" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E23" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F23" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B24" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C24" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D24" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E24" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F24" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B25" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C25" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D25" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E25" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F25" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B26" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C26" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D26" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E26" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F26" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B27" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C27" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D27" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E27" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F27" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B28" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C28" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D28" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E28" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F28" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B29" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C29" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E29" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F29" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B30" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C30" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E30" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F30" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B31" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C31" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D31" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
